--- a/docs/planning/요구사항 정의서_6기_5팀_v1.3.xlsx
+++ b/docs/planning/요구사항 정의서_6기_5팀_v1.3.xlsx
@@ -774,6 +774,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="10" t="inlineStr">
         <is>
@@ -902,7 +903,7 @@
       </c>
       <c r="B13" s="35" t="inlineStr">
         <is>
-          <t>MVP = 스프린트 안에 반드시 만드는 것 / 후순위 = MVP 끝난 뒤. v1.3 기준 제안값이며 9/29 스프린트 회의에서 확정</t>
+          <t>MVP = 스프린트 안에 반드시 만드는 것 / 후순위 = MVP 끝난 뒤. v1.3 기준 제안값이며 9/28 16시 오후 미팅에서 확정</t>
         </is>
       </c>
     </row>
@@ -3085,7 +3086,7 @@
       </c>
       <c r="D108" s="42" t="inlineStr">
         <is>
-          <t>파기 범위 제안 v1.3 — 9/29 팀 확인 · 우선순위 조정: 개인정보</t>
+          <t>파기 범위 제안 v1.3 — 9/28 16시 오후 미팅 확인 · 우선순위 조정: 개인정보</t>
         </is>
       </c>
       <c r="E108" s="42" t="n"/>
@@ -3183,7 +3184,7 @@
         <is>
           <t>N열 "MVP (제안)" 추가: 후순위 11건 (REQ-015 · 076~079 · 100 · 101 · 113 · 114 · 116 · 117), 나머지 MVP
 MVP 흐름: 업로드 → OCR 확인 → 분석 → 결과 → 결과 연계 챗봇 + 실천 목표 선택 · 체크
-사유: 4주 일정에 45개 화면은 과다 (리뷰 지적 4) — 9/29 스프린트 회의에서 확정</t>
+사유: 4주 일정에 45개 화면은 과다 (리뷰 지적 4) — 9/28 16시 오후 미팅에서 확정</t>
         </is>
       </c>
       <c r="E113" s="42" t="n"/>
@@ -3315,6 +3316,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -3704,6 +3706,7 @@
         <v/>
       </c>
     </row>
+    <row r="12"/>
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
@@ -3803,6 +3806,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4370,7 +4374,7 @@
       </c>
       <c r="M11" s="22" t="inlineStr">
         <is>
-          <t>파기 범위 제안 v1.3 — 9/29 팀 확인 · 우선순위 조정: 개인정보</t>
+          <t>파기 범위 제안 v1.3 — 9/28 16시 오후 미팅 확인 · 우선순위 조정: 개인정보</t>
         </is>
       </c>
       <c r="N11" s="46" t="inlineStr">
@@ -4869,6 +4873,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -6371,6 +6376,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -8505,6 +8511,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -9355,6 +9362,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -10065,6 +10073,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
